--- a/artfynd/A 63661-2025 artfynd.xlsx
+++ b/artfynd/A 63661-2025 artfynd.xlsx
@@ -2014,10 +2014,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130874765</v>
+        <v>130864526</v>
       </c>
       <c r="B14" t="n">
-        <v>57864</v>
+        <v>83201</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,49 +2025,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>446077</v>
+        <v>445972</v>
       </c>
       <c r="R14" t="n">
-        <v>7030802</v>
+        <v>7031064</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2096,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2106,12 +2094,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Hona på avskalad mindre gran, se bilder.</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2120,50 +2108,51 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130864526</v>
+        <v>130864509</v>
       </c>
       <c r="B15" t="n">
-        <v>83201</v>
+        <v>80292</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>229748</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2173,13 +2162,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445972</v>
+        <v>445988</v>
       </c>
       <c r="R15" t="n">
-        <v>7031064</v>
+        <v>7031220</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2208,7 +2197,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2218,12 +2207,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På kalkblock i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2232,7 +2221,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2251,32 +2239,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130864509</v>
+        <v>130864510</v>
       </c>
       <c r="B16" t="n">
-        <v>80292</v>
+        <v>78233</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229748</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2286,13 +2274,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445988</v>
+        <v>445990</v>
       </c>
       <c r="R16" t="n">
         <v>7031220</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2321,7 +2309,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2331,12 +2319,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På kalkblock i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2363,10 +2351,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130864510</v>
+        <v>130864515</v>
       </c>
       <c r="B17" t="n">
-        <v>78233</v>
+        <v>83201</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2374,21 +2362,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2398,13 +2386,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445990</v>
+        <v>445932</v>
       </c>
       <c r="R17" t="n">
-        <v>7031220</v>
+        <v>7031103</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2433,7 +2421,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2443,12 +2431,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2475,32 +2463,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130864515</v>
+        <v>130864521</v>
       </c>
       <c r="B18" t="n">
-        <v>83201</v>
+        <v>91739</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2510,13 +2498,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445932</v>
+        <v>446069</v>
       </c>
       <c r="R18" t="n">
-        <v>7031103</v>
+        <v>7030939</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2545,7 +2533,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2555,12 +2543,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På död klen gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2587,48 +2575,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130864521</v>
+        <v>130864691</v>
       </c>
       <c r="B19" t="n">
-        <v>91739</v>
+        <v>83201</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Landverk, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446069</v>
+        <v>445968</v>
       </c>
       <c r="R19" t="n">
-        <v>7030939</v>
+        <v>7031095</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2657,7 +2645,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2667,12 +2655,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På död klen gran i gammal granskog</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2687,22 +2670,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130864691</v>
+        <v>130874549</v>
       </c>
       <c r="B20" t="n">
-        <v>83201</v>
+        <v>58023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2710,34 +2693,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445968</v>
+        <v>446061</v>
       </c>
       <c r="R20" t="n">
-        <v>7031095</v>
+        <v>7030824</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -2769,7 +2752,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2779,7 +2762,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2794,12 +2782,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2918,32 +2906,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130874549</v>
+        <v>130864524</v>
       </c>
       <c r="B22" t="n">
-        <v>58023</v>
+        <v>91739</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2953,13 +2941,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446061</v>
+        <v>446021</v>
       </c>
       <c r="R22" t="n">
-        <v>7030824</v>
+        <v>7031024</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2988,7 +2976,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2998,12 +2986,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>På döda grenar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3018,44 +3006,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130864524</v>
+        <v>130864518</v>
       </c>
       <c r="B23" t="n">
-        <v>91739</v>
+        <v>83201</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3065,13 +3053,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446021</v>
+        <v>446031</v>
       </c>
       <c r="R23" t="n">
-        <v>7031024</v>
+        <v>7030902</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3100,7 +3088,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3110,12 +3098,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3142,10 +3130,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130864518</v>
+        <v>130864530</v>
       </c>
       <c r="B24" t="n">
-        <v>83201</v>
+        <v>79221</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3153,21 +3141,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3177,13 +3165,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>446031</v>
+        <v>445967</v>
       </c>
       <c r="R24" t="n">
-        <v>7030902</v>
+        <v>7031099</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3212,7 +3200,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3222,12 +3210,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran (ca 150 år)i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3254,7 +3242,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130864530</v>
+        <v>130874548</v>
       </c>
       <c r="B25" t="n">
         <v>79221</v>
@@ -3283,19 +3271,22 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445967</v>
+        <v>446058</v>
       </c>
       <c r="R25" t="n">
-        <v>7031099</v>
+        <v>7030768</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3324,7 +3315,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3334,12 +3325,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 150 år)i gammal granskog</t>
+          <t>Rikligt med mindre bålar, ca 150-200 på en gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,28 +3339,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130874548</v>
+        <v>130864508</v>
       </c>
       <c r="B26" t="n">
-        <v>79221</v>
+        <v>83201</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3377,40 +3369,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446058</v>
+        <v>445980</v>
       </c>
       <c r="R26" t="n">
-        <v>7030768</v>
+        <v>7031237</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3439,7 +3428,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3449,12 +3438,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt med mindre bålar, ca 150-200 på en gran.</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3463,26 +3452,25 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130864508</v>
+        <v>130864686</v>
       </c>
       <c r="B27" t="n">
         <v>83201</v>
@@ -3513,17 +3501,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Landverk, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445980</v>
+        <v>445975</v>
       </c>
       <c r="R27" t="n">
-        <v>7031237</v>
+        <v>7031174</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3552,7 +3540,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3562,12 +3550,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3582,22 +3565,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130864686</v>
+        <v>130864512</v>
       </c>
       <c r="B28" t="n">
-        <v>83201</v>
+        <v>79221</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3605,37 +3588,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445975</v>
+        <v>445966</v>
       </c>
       <c r="R28" t="n">
-        <v>7031174</v>
+        <v>7031121</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3664,7 +3656,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3674,7 +3666,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På gammal senvuxen gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3689,19 +3686,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130864512</v>
+        <v>130864692</v>
       </c>
       <c r="B29" t="n">
         <v>79221</v>
@@ -3729,29 +3726,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Landverk, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445966</v>
+        <v>445964</v>
       </c>
       <c r="R29" t="n">
-        <v>7031121</v>
+        <v>7031159</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3780,7 +3768,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3790,12 +3778,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På gammal senvuxen gran i gammal granskog</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3810,22 +3793,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130864692</v>
+        <v>130874765</v>
       </c>
       <c r="B30" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3833,37 +3816,53 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445964</v>
+        <v>446077</v>
       </c>
       <c r="R30" t="n">
-        <v>7031159</v>
+        <v>7030802</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3892,7 +3891,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3902,7 +3901,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Hona på avskalad mindre gran, se bilder.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3917,12 +3921,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 63661-2025 artfynd.xlsx
+++ b/artfynd/A 63661-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130864516</v>
+        <v>130874764</v>
       </c>
       <c r="B2" t="n">
-        <v>91739</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445965</v>
+        <v>445900</v>
       </c>
       <c r="R2" t="n">
-        <v>7031017</v>
+        <v>7030781</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran i gammal granskog</t>
+          <t>Liten, på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,60 +775,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130874764</v>
+        <v>130864688</v>
       </c>
       <c r="B3" t="n">
-        <v>79221</v>
+        <v>80286</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Landverk, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445900</v>
+        <v>446042</v>
       </c>
       <c r="R3" t="n">
-        <v>7030781</v>
+        <v>7030829</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Liten, på gran</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,23 +878,33 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Salix ev jolster</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Salix ev jolster</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130864511</v>
+        <v>130864687</v>
       </c>
       <c r="B4" t="n">
         <v>83201</v>
@@ -930,17 +935,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Landverk, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>445985</v>
       </c>
       <c r="R4" t="n">
-        <v>7031157</v>
+        <v>7030968</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,19 +999,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130864513</v>
+        <v>130864689</v>
       </c>
       <c r="B5" t="n">
         <v>78233</v>
@@ -1042,14 +1042,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Landverk, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445962</v>
+        <v>446026</v>
       </c>
       <c r="R5" t="n">
-        <v>7031114</v>
+        <v>7031030</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,44 +1106,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130864688</v>
+        <v>130864691</v>
       </c>
       <c r="B6" t="n">
-        <v>80286</v>
+        <v>83201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229497</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>446042</v>
+        <v>445968</v>
       </c>
       <c r="R6" t="n">
-        <v>7030829</v>
+        <v>7031095</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1193,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,16 +1209,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>Salix ev jolster</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix ev jolster</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1240,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130864514</v>
+        <v>130874549</v>
       </c>
       <c r="B7" t="n">
-        <v>83201</v>
+        <v>58023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1236,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445944</v>
+        <v>446061</v>
       </c>
       <c r="R7" t="n">
-        <v>7031101</v>
+        <v>7030824</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1310,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,12 +1305,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,22 +1325,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130864687</v>
+        <v>130874548</v>
       </c>
       <c r="B8" t="n">
-        <v>83201</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,37 +1348,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445985</v>
+        <v>446058</v>
       </c>
       <c r="R8" t="n">
-        <v>7030968</v>
+        <v>7030768</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1410,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1420,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt med mindre bålar, ca 150-200 på en gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,28 +1434,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130864689</v>
+        <v>130864686</v>
       </c>
       <c r="B9" t="n">
-        <v>78233</v>
+        <v>83201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,21 +1464,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>446026</v>
+        <v>445975</v>
       </c>
       <c r="R9" t="n">
-        <v>7031030</v>
+        <v>7031174</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1529,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,10 +1560,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130864529</v>
+        <v>130864692</v>
       </c>
       <c r="B10" t="n">
-        <v>78233</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1577,37 +1571,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Landverk, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445967</v>
+        <v>445964</v>
       </c>
       <c r="R10" t="n">
-        <v>7031099</v>
+        <v>7031159</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1636,7 +1630,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1646,12 +1640,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1666,22 +1655,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130864522</v>
+        <v>130874765</v>
       </c>
       <c r="B11" t="n">
-        <v>78233</v>
+        <v>57864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,37 +1678,53 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446025</v>
+        <v>446077</v>
       </c>
       <c r="R11" t="n">
-        <v>7031011</v>
+        <v>7030802</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1758,12 +1763,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Hona på avskalad mindre gran, se bilder.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1778,44 +1783,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130864519</v>
+        <v>130864516</v>
       </c>
       <c r="B12" t="n">
-        <v>83201</v>
+        <v>91739</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>446074</v>
+        <v>445965</v>
       </c>
       <c r="R12" t="n">
-        <v>7030848</v>
+        <v>7031017</v>
       </c>
       <c r="S12" t="n">
         <v>6</v>
@@ -1860,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1870,12 +1875,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På död gren på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130864525</v>
+        <v>130864511</v>
       </c>
       <c r="B13" t="n">
-        <v>78233</v>
+        <v>83201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,37 +1918,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>446018</v>
+        <v>445985</v>
       </c>
       <c r="R13" t="n">
-        <v>7031025</v>
+        <v>7031157</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1979,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,7 +1989,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1996,6 +2003,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2014,10 +2022,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130864526</v>
+        <v>130864513</v>
       </c>
       <c r="B14" t="n">
-        <v>83201</v>
+        <v>78233</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,37 +2033,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445972</v>
+        <v>445962</v>
       </c>
       <c r="R14" t="n">
-        <v>7031064</v>
+        <v>7031114</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2127,48 +2137,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130864509</v>
+        <v>130864514</v>
       </c>
       <c r="B15" t="n">
-        <v>80292</v>
+        <v>83201</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229748</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445988</v>
+        <v>445944</v>
       </c>
       <c r="R15" t="n">
-        <v>7031220</v>
+        <v>7031101</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2197,7 +2209,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2207,12 +2219,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På kalkblock i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2221,6 +2233,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2239,7 +2252,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130864510</v>
+        <v>130864529</v>
       </c>
       <c r="B16" t="n">
         <v>78233</v>
@@ -2274,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445990</v>
+        <v>445967</v>
       </c>
       <c r="R16" t="n">
-        <v>7031220</v>
+        <v>7031099</v>
       </c>
       <c r="S16" t="n">
         <v>6</v>
@@ -2309,7 +2322,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2319,7 +2332,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2351,10 +2364,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130864515</v>
+        <v>130864522</v>
       </c>
       <c r="B17" t="n">
-        <v>83201</v>
+        <v>78233</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2362,21 +2375,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2386,13 +2399,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445932</v>
+        <v>446025</v>
       </c>
       <c r="R17" t="n">
-        <v>7031103</v>
+        <v>7031011</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2421,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2431,12 +2444,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2463,32 +2476,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130864521</v>
+        <v>130864519</v>
       </c>
       <c r="B18" t="n">
-        <v>91739</v>
+        <v>83201</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2498,13 +2511,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446069</v>
+        <v>446074</v>
       </c>
       <c r="R18" t="n">
-        <v>7030939</v>
+        <v>7030848</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2533,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2543,12 +2556,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På död klen gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2575,10 +2588,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130864691</v>
+        <v>130864525</v>
       </c>
       <c r="B19" t="n">
-        <v>83201</v>
+        <v>78233</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2586,37 +2599,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445968</v>
+        <v>446018</v>
       </c>
       <c r="R19" t="n">
-        <v>7031095</v>
+        <v>7031025</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2645,7 +2658,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2655,7 +2668,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2670,22 +2688,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130874549</v>
+        <v>130864526</v>
       </c>
       <c r="B20" t="n">
-        <v>58023</v>
+        <v>83201</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2693,21 +2711,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2717,13 +2735,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>446061</v>
+        <v>445972</v>
       </c>
       <c r="R20" t="n">
-        <v>7030824</v>
+        <v>7031064</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2752,7 +2770,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2762,12 +2780,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2776,66 +2794,69 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130864528</v>
+        <v>130864509</v>
       </c>
       <c r="B21" t="n">
-        <v>79221</v>
+        <v>80292</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445965</v>
+        <v>445988</v>
       </c>
       <c r="R21" t="n">
-        <v>7031090</v>
+        <v>7031220</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2864,7 +2885,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2874,12 +2895,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På kalkblock i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2888,6 +2909,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2906,45 +2928,47 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130864524</v>
+        <v>130864510</v>
       </c>
       <c r="B22" t="n">
-        <v>91739</v>
+        <v>78233</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446021</v>
+        <v>445990</v>
       </c>
       <c r="R22" t="n">
-        <v>7031024</v>
+        <v>7031220</v>
       </c>
       <c r="S22" t="n">
         <v>6</v>
@@ -2976,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2986,12 +3010,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3000,6 +3024,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3018,7 +3043,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130864518</v>
+        <v>130864515</v>
       </c>
       <c r="B23" t="n">
         <v>83201</v>
@@ -3047,19 +3072,21 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446031</v>
+        <v>445932</v>
       </c>
       <c r="R23" t="n">
-        <v>7030902</v>
+        <v>7031103</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3088,7 +3115,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3098,12 +3125,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3112,6 +3139,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3130,32 +3158,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130864530</v>
+        <v>130864521</v>
       </c>
       <c r="B24" t="n">
-        <v>79221</v>
+        <v>91739</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3165,13 +3193,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445967</v>
+        <v>446069</v>
       </c>
       <c r="R24" t="n">
-        <v>7031099</v>
+        <v>7030939</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3200,7 +3228,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3210,12 +3238,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 150 år)i gammal granskog</t>
+          <t>På död klen gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3242,7 +3270,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130874548</v>
+        <v>130864528</v>
       </c>
       <c r="B25" t="n">
         <v>79221</v>
@@ -3271,22 +3299,19 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446058</v>
+        <v>445965</v>
       </c>
       <c r="R25" t="n">
-        <v>7030768</v>
+        <v>7031090</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3315,7 +3340,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3325,12 +3350,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt med mindre bålar, ca 150-200 på en gran.</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3339,51 +3364,50 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130864508</v>
+        <v>130864524</v>
       </c>
       <c r="B26" t="n">
-        <v>83201</v>
+        <v>91739</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3393,10 +3417,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445980</v>
+        <v>446021</v>
       </c>
       <c r="R26" t="n">
-        <v>7031237</v>
+        <v>7031024</v>
       </c>
       <c r="S26" t="n">
         <v>6</v>
@@ -3428,7 +3452,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3438,12 +3462,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På döda grenar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3470,7 +3494,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130864686</v>
+        <v>130864518</v>
       </c>
       <c r="B27" t="n">
         <v>83201</v>
@@ -3501,17 +3525,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445975</v>
+        <v>446031</v>
       </c>
       <c r="R27" t="n">
-        <v>7031174</v>
+        <v>7030902</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3540,7 +3564,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3550,7 +3574,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3565,19 +3594,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130864512</v>
+        <v>130864530</v>
       </c>
       <c r="B28" t="n">
         <v>79221</v>
@@ -3605,26 +3634,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445966</v>
+        <v>445967</v>
       </c>
       <c r="R28" t="n">
-        <v>7031121</v>
+        <v>7031099</v>
       </c>
       <c r="S28" t="n">
         <v>6</v>
@@ -3656,7 +3676,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3666,12 +3686,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal senvuxen gran i gammal granskog</t>
+          <t>På gammal gran (ca 150 år)i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3698,10 +3718,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130864692</v>
+        <v>130864508</v>
       </c>
       <c r="B29" t="n">
-        <v>79221</v>
+        <v>83201</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3709,37 +3729,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445964</v>
+        <v>445980</v>
       </c>
       <c r="R29" t="n">
-        <v>7031159</v>
+        <v>7031237</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3768,7 +3790,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3778,7 +3800,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3787,28 +3814,29 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130874765</v>
+        <v>130864512</v>
       </c>
       <c r="B30" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3816,39 +3844,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3856,13 +3879,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446077</v>
+        <v>445966</v>
       </c>
       <c r="R30" t="n">
-        <v>7030802</v>
+        <v>7031121</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3891,7 +3914,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3901,12 +3924,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Hona på avskalad mindre gran, se bilder.</t>
+          <t>På gammal senvuxen gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3915,18 +3938,19 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 63661-2025 artfynd.xlsx
+++ b/artfynd/A 63661-2025 artfynd.xlsx
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130864514</v>
+        <v>130864513</v>
       </c>
       <c r="B13" t="n">
-        <v>83224</v>
+        <v>78256</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445944</v>
+        <v>445962</v>
       </c>
       <c r="R13" t="n">
-        <v>7031101</v>
+        <v>7031114</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2022,7 +2022,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130864511</v>
+        <v>130864514</v>
       </c>
       <c r="B14" t="n">
         <v>83224</v>
@@ -2059,13 +2059,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445985</v>
+        <v>445944</v>
       </c>
       <c r="R14" t="n">
-        <v>7031157</v>
+        <v>7031101</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2137,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130864513</v>
+        <v>130864511</v>
       </c>
       <c r="B15" t="n">
-        <v>78256</v>
+        <v>83224</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2174,13 +2174,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445962</v>
+        <v>445985</v>
       </c>
       <c r="R15" t="n">
-        <v>7031114</v>
+        <v>7031157</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2928,50 +2928,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130864515</v>
+        <v>130864521</v>
       </c>
       <c r="B22" t="n">
-        <v>83224</v>
+        <v>91772</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445932</v>
+        <v>446069</v>
       </c>
       <c r="R22" t="n">
-        <v>7031103</v>
+        <v>7030939</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3000,7 +2998,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,12 +3008,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På död klen gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3024,7 +3022,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3043,48 +3040,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130864521</v>
+        <v>130864510</v>
       </c>
       <c r="B23" t="n">
-        <v>91772</v>
+        <v>78256</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446069</v>
+        <v>445990</v>
       </c>
       <c r="R23" t="n">
-        <v>7030939</v>
+        <v>7031220</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3113,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3123,12 +3122,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På död klen gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3137,6 +3136,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3155,10 +3155,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130864510</v>
+        <v>130864515</v>
       </c>
       <c r="B24" t="n">
-        <v>78256</v>
+        <v>83224</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3166,21 +3166,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445990</v>
+        <v>445932</v>
       </c>
       <c r="R24" t="n">
-        <v>7031220</v>
+        <v>7031103</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3494,10 +3494,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130864530</v>
+        <v>130864518</v>
       </c>
       <c r="B27" t="n">
-        <v>79244</v>
+        <v>83224</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3505,21 +3505,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3529,13 +3529,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445967</v>
+        <v>446031</v>
       </c>
       <c r="R27" t="n">
-        <v>7031099</v>
+        <v>7030902</v>
       </c>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 150 år)i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3606,10 +3606,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130864518</v>
+        <v>130864530</v>
       </c>
       <c r="B28" t="n">
-        <v>83224</v>
+        <v>79244</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>446031</v>
+        <v>445967</v>
       </c>
       <c r="R28" t="n">
-        <v>7030902</v>
+        <v>7031099</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3686,12 +3686,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran (ca 150 år)i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 63661-2025 artfynd.xlsx
+++ b/artfynd/A 63661-2025 artfynd.xlsx
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130864513</v>
+        <v>130864511</v>
       </c>
       <c r="B13" t="n">
-        <v>78256</v>
+        <v>83224</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1944,13 +1944,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445962</v>
+        <v>445985</v>
       </c>
       <c r="R13" t="n">
-        <v>7031114</v>
+        <v>7031157</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2137,10 +2137,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130864511</v>
+        <v>130864513</v>
       </c>
       <c r="B15" t="n">
-        <v>83224</v>
+        <v>78256</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,21 +2148,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2174,13 +2174,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445985</v>
+        <v>445962</v>
       </c>
       <c r="R15" t="n">
-        <v>7031157</v>
+        <v>7031114</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">

--- a/artfynd/A 63661-2025 artfynd.xlsx
+++ b/artfynd/A 63661-2025 artfynd.xlsx
@@ -2928,48 +2928,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130864521</v>
+        <v>130864510</v>
       </c>
       <c r="B22" t="n">
-        <v>91772</v>
+        <v>78256</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446069</v>
+        <v>445990</v>
       </c>
       <c r="R22" t="n">
-        <v>7030939</v>
+        <v>7031220</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2998,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3008,12 +3010,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På död klen gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3022,6 +3024,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3040,50 +3043,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130864510</v>
+        <v>130864521</v>
       </c>
       <c r="B23" t="n">
-        <v>78256</v>
+        <v>91772</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445990</v>
+        <v>446069</v>
       </c>
       <c r="R23" t="n">
-        <v>7031220</v>
+        <v>7030939</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3112,7 +3113,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,12 +3123,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På död klen gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3136,7 +3137,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 63661-2025 artfynd.xlsx
+++ b/artfynd/A 63661-2025 artfynd.xlsx
@@ -1798,7 +1798,7 @@
         <v>130864516</v>
       </c>
       <c r="B12" t="n">
-        <v>91772</v>
+        <v>91773</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>130864511</v>
       </c>
       <c r="B13" t="n">
-        <v>83224</v>
+        <v>83225</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>130864514</v>
       </c>
       <c r="B14" t="n">
-        <v>83224</v>
+        <v>83225</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>130864513</v>
       </c>
       <c r="B15" t="n">
-        <v>78256</v>
+        <v>78257</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
         <v>130864529</v>
       </c>
       <c r="B16" t="n">
-        <v>78256</v>
+        <v>78257</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2364,10 +2364,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130864519</v>
+        <v>130864522</v>
       </c>
       <c r="B17" t="n">
-        <v>83224</v>
+        <v>78257</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2375,21 +2375,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446074</v>
+        <v>446025</v>
       </c>
       <c r="R17" t="n">
-        <v>7030848</v>
+        <v>7031011</v>
       </c>
       <c r="S17" t="n">
         <v>6</v>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2476,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130864522</v>
+        <v>130864519</v>
       </c>
       <c r="B18" t="n">
-        <v>78256</v>
+        <v>83225</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,21 +2487,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446025</v>
+        <v>446074</v>
       </c>
       <c r="R18" t="n">
-        <v>7031011</v>
+        <v>7030848</v>
       </c>
       <c r="S18" t="n">
         <v>6</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2591,7 +2591,7 @@
         <v>130864525</v>
       </c>
       <c r="B19" t="n">
-        <v>78256</v>
+        <v>78257</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>130864526</v>
       </c>
       <c r="B20" t="n">
-        <v>83224</v>
+        <v>83225</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>130864509</v>
       </c>
       <c r="B21" t="n">
-        <v>80315</v>
+        <v>80316</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>130864510</v>
       </c>
       <c r="B22" t="n">
-        <v>78256</v>
+        <v>78257</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>130864521</v>
       </c>
       <c r="B23" t="n">
-        <v>91772</v>
+        <v>91773</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>130864515</v>
       </c>
       <c r="B24" t="n">
-        <v>83224</v>
+        <v>83225</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
         <v>130864528</v>
       </c>
       <c r="B25" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
         <v>130864524</v>
       </c>
       <c r="B26" t="n">
-        <v>91772</v>
+        <v>91773</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>130864518</v>
       </c>
       <c r="B27" t="n">
-        <v>83224</v>
+        <v>83225</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         <v>130864530</v>
       </c>
       <c r="B28" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>130864508</v>
       </c>
       <c r="B29" t="n">
-        <v>83224</v>
+        <v>83225</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>130864512</v>
       </c>
       <c r="B30" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 63661-2025 artfynd.xlsx
+++ b/artfynd/A 63661-2025 artfynd.xlsx
@@ -2364,10 +2364,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130864522</v>
+        <v>130864519</v>
       </c>
       <c r="B17" t="n">
-        <v>78257</v>
+        <v>83225</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2375,21 +2375,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446025</v>
+        <v>446074</v>
       </c>
       <c r="R17" t="n">
-        <v>7031011</v>
+        <v>7030848</v>
       </c>
       <c r="S17" t="n">
         <v>6</v>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2476,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130864519</v>
+        <v>130864522</v>
       </c>
       <c r="B18" t="n">
-        <v>83225</v>
+        <v>78257</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,21 +2487,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446074</v>
+        <v>446025</v>
       </c>
       <c r="R18" t="n">
-        <v>7030848</v>
+        <v>7031011</v>
       </c>
       <c r="S18" t="n">
         <v>6</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2700,48 +2700,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130864526</v>
+        <v>130864509</v>
       </c>
       <c r="B20" t="n">
-        <v>83225</v>
+        <v>80316</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>229748</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445972</v>
+        <v>445988</v>
       </c>
       <c r="R20" t="n">
-        <v>7031064</v>
+        <v>7031220</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2770,7 +2772,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2780,12 +2782,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På kalkblock i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,50 +2815,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130864509</v>
+        <v>130864526</v>
       </c>
       <c r="B21" t="n">
-        <v>80316</v>
+        <v>83225</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229748</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445988</v>
+        <v>445972</v>
       </c>
       <c r="R21" t="n">
-        <v>7031220</v>
+        <v>7031064</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2895,12 +2895,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På kalkblock i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 63661-2025 artfynd.xlsx
+++ b/artfynd/A 63661-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130874764</v>
+        <v>130864516</v>
       </c>
       <c r="B2" t="n">
-        <v>79244</v>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445900</v>
+        <v>445965</v>
       </c>
       <c r="R2" t="n">
-        <v>7030781</v>
+        <v>7031017</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Liten, på gran</t>
+          <t>På död gren på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130864688</v>
+        <v>130864521</v>
       </c>
       <c r="B3" t="n">
-        <v>80309</v>
+        <v>91872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,37 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446042</v>
+        <v>446069</v>
       </c>
       <c r="R3" t="n">
-        <v>7030829</v>
+        <v>7030939</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På död klen gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,74 +883,64 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Salix ev jolster</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Salix ev jolster</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130864687</v>
+        <v>130864524</v>
       </c>
       <c r="B4" t="n">
-        <v>83224</v>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445985</v>
+        <v>446021</v>
       </c>
       <c r="R4" t="n">
-        <v>7030968</v>
+        <v>7031024</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På döda grenar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,60 +999,71 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130864689</v>
+        <v>130864512</v>
       </c>
       <c r="B5" t="n">
-        <v>78256</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446026</v>
+        <v>445966</v>
       </c>
       <c r="R5" t="n">
-        <v>7031030</v>
+        <v>7031121</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,7 +1092,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1102,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gammal senvuxen gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,66 +1116,67 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130864691</v>
+        <v>130864528</v>
       </c>
       <c r="B6" t="n">
-        <v>83224</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445968</v>
+        <v>445965</v>
       </c>
       <c r="R6" t="n">
-        <v>7031095</v>
+        <v>7031090</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1188,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1215,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,44 +1235,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130874549</v>
+        <v>130864530</v>
       </c>
       <c r="B7" t="n">
-        <v>58043</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,13 +1282,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>446061</v>
+        <v>445967</v>
       </c>
       <c r="R7" t="n">
-        <v>7030824</v>
+        <v>7031099</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,12 +1327,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>På gammal gran (ca 150 år)i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,26 +1347,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130874548</v>
+        <v>130864692</v>
       </c>
       <c r="B8" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1366,19 +1388,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Landverk, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>446058</v>
+        <v>445964</v>
       </c>
       <c r="R8" t="n">
-        <v>7030768</v>
+        <v>7031159</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1410,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1420,12 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt med mindre bålar, ca 150-200 på en gran.</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,64 +1448,66 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130864686</v>
+        <v>130874548</v>
       </c>
       <c r="B9" t="n">
-        <v>83224</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445975</v>
+        <v>446058</v>
       </c>
       <c r="R9" t="n">
-        <v>7031174</v>
+        <v>7030768</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1523,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1549,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt med mindre bålar, ca 150-200 på en gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,32 +1563,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130864692</v>
+        <v>130874764</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1591,17 +1613,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445964</v>
+        <v>445900</v>
       </c>
       <c r="R10" t="n">
-        <v>7031159</v>
+        <v>7030781</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1630,7 +1652,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1640,7 +1662,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Liten, på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,22 +1682,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130874765</v>
+        <v>130864508</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,39 +1705,25 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1718,13 +1731,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>446077</v>
+        <v>445980</v>
       </c>
       <c r="R11" t="n">
-        <v>7030802</v>
+        <v>7031237</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,7 +1766,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,12 +1776,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Hona på avskalad mindre gran, se bilder.</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1777,66 +1790,69 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130864516</v>
+        <v>130864511</v>
       </c>
       <c r="B12" t="n">
-        <v>91773</v>
+        <v>83307</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445965</v>
+        <v>445985</v>
       </c>
       <c r="R12" t="n">
-        <v>7031017</v>
+        <v>7031157</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1865,7 +1881,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,12 +1891,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På död gren på gammal levande gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1889,6 +1905,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1907,10 +1924,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130864511</v>
+        <v>130864514</v>
       </c>
       <c r="B13" t="n">
-        <v>83225</v>
+        <v>83307</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1944,13 +1961,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445985</v>
+        <v>445944</v>
       </c>
       <c r="R13" t="n">
-        <v>7031157</v>
+        <v>7031101</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1979,7 +1996,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1989,7 +2006,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2022,10 +2039,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130864514</v>
+        <v>130864515</v>
       </c>
       <c r="B14" t="n">
-        <v>83225</v>
+        <v>83307</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,13 +2076,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445944</v>
+        <v>445932</v>
       </c>
       <c r="R14" t="n">
-        <v>7031101</v>
+        <v>7031103</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2094,7 +2111,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,12 +2121,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2137,10 +2154,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130864513</v>
+        <v>130864518</v>
       </c>
       <c r="B15" t="n">
-        <v>78257</v>
+        <v>83307</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2148,39 +2165,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445962</v>
+        <v>446031</v>
       </c>
       <c r="R15" t="n">
-        <v>7031114</v>
+        <v>7030902</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2209,7 +2224,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2219,7 +2234,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2233,7 +2248,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2252,10 +2266,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130864529</v>
+        <v>130864519</v>
       </c>
       <c r="B16" t="n">
-        <v>78257</v>
+        <v>83307</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,21 +2277,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2287,10 +2301,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445967</v>
+        <v>446074</v>
       </c>
       <c r="R16" t="n">
-        <v>7031099</v>
+        <v>7030848</v>
       </c>
       <c r="S16" t="n">
         <v>6</v>
@@ -2322,7 +2336,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2332,7 +2346,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2364,10 +2378,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130864519</v>
+        <v>130864526</v>
       </c>
       <c r="B17" t="n">
-        <v>83225</v>
+        <v>83307</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2399,10 +2413,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>446074</v>
+        <v>445972</v>
       </c>
       <c r="R17" t="n">
-        <v>7030848</v>
+        <v>7031064</v>
       </c>
       <c r="S17" t="n">
         <v>6</v>
@@ -2434,7 +2448,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2444,7 +2458,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2458,6 +2472,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2476,10 +2491,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130864522</v>
+        <v>130864686</v>
       </c>
       <c r="B18" t="n">
-        <v>78257</v>
+        <v>83307</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,37 +2502,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Landverk, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>446025</v>
+        <v>445975</v>
       </c>
       <c r="R18" t="n">
-        <v>7031011</v>
+        <v>7031174</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2546,7 +2561,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,12 +2571,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2576,22 +2586,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130864525</v>
+        <v>130864687</v>
       </c>
       <c r="B19" t="n">
-        <v>78257</v>
+        <v>83307</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,37 +2609,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Landverk, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>446018</v>
+        <v>445985</v>
       </c>
       <c r="R19" t="n">
-        <v>7031025</v>
+        <v>7030968</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2658,7 +2668,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,12 +2678,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2688,62 +2693,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130864509</v>
+        <v>130864691</v>
       </c>
       <c r="B20" t="n">
-        <v>80316</v>
+        <v>83307</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229748</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Landverk, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445988</v>
+        <v>445968</v>
       </c>
       <c r="R20" t="n">
-        <v>7031220</v>
+        <v>7031095</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2772,7 +2775,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2782,12 +2785,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:32</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På kalkblock i gammal granskog</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2796,29 +2794,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130864526</v>
+        <v>130874765</v>
       </c>
       <c r="B21" t="n">
-        <v>83225</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2826,37 +2823,53 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445972</v>
+        <v>446077</v>
       </c>
       <c r="R21" t="n">
-        <v>7031064</v>
+        <v>7030802</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2885,7 +2898,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2895,12 +2908,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Hona på avskalad mindre gran, se bilder.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2909,29 +2922,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130864510</v>
+        <v>130874549</v>
       </c>
       <c r="B22" t="n">
-        <v>78257</v>
+        <v>58114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2939,39 +2951,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445990</v>
+        <v>446061</v>
       </c>
       <c r="R22" t="n">
-        <v>7031220</v>
+        <v>7030824</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3000,7 +3010,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,12 +3020,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3024,51 +3034,50 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130864521</v>
+        <v>130864523</v>
       </c>
       <c r="B23" t="n">
-        <v>91773</v>
+        <v>78333</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>228575</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brun svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis epithallina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3078,13 +3087,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>446069</v>
+        <v>446021</v>
       </c>
       <c r="R23" t="n">
-        <v>7030939</v>
+        <v>7031024</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3113,7 +3122,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3123,12 +3132,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På död klen gran i gammal granskog</t>
+          <t>På bålen av grå nållav på bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3155,10 +3164,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130864515</v>
+        <v>130864510</v>
       </c>
       <c r="B24" t="n">
-        <v>83225</v>
+        <v>78339</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3166,21 +3175,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3192,13 +3201,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445932</v>
+        <v>445990</v>
       </c>
       <c r="R24" t="n">
-        <v>7031103</v>
+        <v>7031220</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3227,7 +3236,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3237,12 +3246,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3270,10 +3279,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130864528</v>
+        <v>130864513</v>
       </c>
       <c r="B25" t="n">
-        <v>79245</v>
+        <v>78339</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3281,37 +3290,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Landverk, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445965</v>
+        <v>445962</v>
       </c>
       <c r="R25" t="n">
-        <v>7031090</v>
+        <v>7031114</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3340,7 +3351,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3350,12 +3361,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3364,6 +3375,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3382,32 +3394,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130864524</v>
+        <v>130864522</v>
       </c>
       <c r="B26" t="n">
-        <v>91773</v>
+        <v>78339</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>228579</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3417,10 +3429,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>446021</v>
+        <v>446025</v>
       </c>
       <c r="R26" t="n">
-        <v>7031024</v>
+        <v>7031011</v>
       </c>
       <c r="S26" t="n">
         <v>6</v>
@@ -3452,7 +3464,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3462,12 +3474,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På döda grenar på gammal levande gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3494,10 +3506,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130864518</v>
+        <v>130864525</v>
       </c>
       <c r="B27" t="n">
-        <v>83225</v>
+        <v>78339</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3505,21 +3517,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3529,13 +3541,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>446031</v>
+        <v>446018</v>
       </c>
       <c r="R27" t="n">
-        <v>7030902</v>
+        <v>7031025</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3564,7 +3576,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3574,7 +3586,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3606,10 +3618,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130864530</v>
+        <v>130864529</v>
       </c>
       <c r="B28" t="n">
-        <v>79245</v>
+        <v>78339</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,21 +3629,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3676,7 +3688,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3686,12 +3698,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal gran (ca 150 år)i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3718,10 +3730,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130864508</v>
+        <v>130864689</v>
       </c>
       <c r="B29" t="n">
-        <v>83225</v>
+        <v>78339</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3729,39 +3741,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Landverk, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445980</v>
+        <v>446026</v>
       </c>
       <c r="R29" t="n">
-        <v>7031237</v>
+        <v>7031030</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3790,7 +3800,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3800,12 +3810,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3814,78 +3819,66 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130864512</v>
+        <v>130864688</v>
       </c>
       <c r="B30" t="n">
-        <v>79245</v>
+        <v>80392</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Landverk, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445966</v>
+        <v>446042</v>
       </c>
       <c r="R30" t="n">
-        <v>7031121</v>
+        <v>7030829</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3914,7 +3907,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3924,12 +3917,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På gammal senvuxen gran i gammal granskog</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3938,22 +3926,146 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>Salix ev jolster</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Salix ev jolster</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130864509</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Landverk, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>445988</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7031220</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På kalkblock i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
           <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
+      <c r="AX31" t="inlineStr">
         <is>
           <t>Jämtlandsskogsgrupp Naturskydsföreningen</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63661-2025 artfynd.xlsx
+++ b/artfynd/A 63661-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864516</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864521</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864524</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864512</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1244,6 +1269,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864528</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1356,6 +1386,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864530</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1463,6 +1498,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864692</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1579,6 +1619,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130874548</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1691,6 +1736,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130874764</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1806,6 +1856,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864508</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1921,6 +1976,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864511</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2036,6 +2096,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864514</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2151,6 +2216,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864515</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2263,6 +2333,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864518</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2375,6 +2450,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864519</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2488,6 +2568,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864526</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2595,6 +2680,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864686</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2702,6 +2792,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864687</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2809,6 +2904,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864691</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2937,6 +3037,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130874765</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3049,6 +3154,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130874549</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3161,6 +3271,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864523</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3276,6 +3391,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864510</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3391,6 +3511,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864513</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3503,6 +3628,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864522</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3615,6 +3745,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864525</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3727,6 +3862,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864529</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3834,6 +3974,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864689</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3951,6 +4096,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864688</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4066,8 +4216,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864509</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>